--- a/proposals/2026-12_nmk-museum-web-maint/정성제안서_평가항목_조견표.xlsx
+++ b/proposals/2026-12_nmk-museum-web-maint/정성제안서_평가항목_조견표.xlsx
@@ -744,7 +744,7 @@
 장애 대응 기준 및 절차
 복합장애 합동 대응 및 장애 예방
 이용자 만족도 조사 · 누리집 모니터링단
-웹 접근성 품질인증 · DB 표준화 · 공공문화정보 연계</t>
+웹 접근성 품질마크 · DB 표준화 · 문화정보 연계</t>
         </is>
       </c>
       <c r="G8" s="5" t="inlineStr"/>
